--- a/results/final_20260514_v2_summary/PlantPseAAC_PartialAbstention_summary.xlsx
+++ b/results/final_20260514_v2_summary/PlantPseAAC_PartialAbstention_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:BU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,100 +476,320 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>afrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>arec__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arec__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>arec__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arec__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>rec__0.0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>rec__0.1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>rec__0.2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>rec__0.3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.3</t>
         </is>
@@ -623,100 +843,320 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.3522±0.0463</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.3217±0.0648</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.3156±0.0779</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.4078±0.0620</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.9838±0.0042</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.9831±0.0037</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.9751±0.0042</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.9458±0.0069</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.5304±0.0697</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.5036±0.0541</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.4050±0.0435</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.2715±0.0362</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5287±0.0701</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5151±0.0574</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.4624±0.0437</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.3887±0.0491</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0.5292±0.0699</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.5074±0.0549</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.4223±0.0419</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.3042±0.0386</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.8531±0.0224</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>0.8342±0.0153</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.7452±0.0317</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.6426±0.0262</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5287±0.0701</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.5034±0.0533</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.4029±0.0432</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.2710±0.0363</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.1907±0.0548</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.2083±0.0777</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.2135±0.0552</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.1886±0.0370</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.1865±0.0491</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.2055±0.0951</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.1818±0.0623</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.1324±0.0275</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.2208±0.0610</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.2484±0.0713</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.3128±0.0664</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.3965±0.0925</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.9868±0.0315</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.9645±0.0491</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.9138±0.0646</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.5884±0.0795</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.5884±0.0525</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.5107±0.0363</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.3689±0.0396</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.5287±0.0701</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.4941±0.0542</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.3790±0.0346</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.2429±0.0306</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.6644±0.0959</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.7302±0.0586</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.7915±0.0725</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.7730±0.0611</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>0.8763±0.0288</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.8572±0.0279</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.7822±0.0356</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>0.6054±0.0479</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>0.5270±0.0706</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.4914±0.0506</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.3488±0.0527</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.1874±0.0367</t>
         </is>
@@ -770,100 +1210,320 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>0.3503±0.0472</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.3178±0.0660</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.3172±0.0776</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.4099±0.0609</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.9839±0.0043</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.9830±0.0038</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.9750±0.0042</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.9454±0.0068</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.5326±0.0713</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.5023±0.0548</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.4041±0.0440</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.2703±0.0352</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.5331±0.0737</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.5161±0.0574</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.4629±0.0450</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.3899±0.0499</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.5322±0.0722</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.5068±0.0553</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.4218±0.0425</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.3034±0.0379</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.8538±0.0234</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.8331±0.0155</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.7441±0.0322</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6396±0.0256</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.5309±0.0718</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.5020±0.0540</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.4020±0.0436</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.2697±0.0353</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.1940±0.0566</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.2083±0.0757</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.2131±0.0548</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.1873±0.0363</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.2031±0.0658</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.2009±0.0919</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.1814±0.0619</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.1313±0.0270</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.2226±0.0615</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.2518±0.0693</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.3132±0.0666</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.3972±0.0927</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.9868±0.0315</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.9626±0.0486</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.9124±0.0642</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.5916±0.0810</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.5873±0.0531</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.5097±0.0367</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.3674±0.0396</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.5305±0.0715</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.4919±0.0552</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.3777±0.0349</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.2414±0.0305</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6696±0.0966</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7316±0.0588</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.7922±0.0730</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7745±0.0617</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>0.8763±0.0288</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.8562±0.0281</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.7816±0.0358</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.6046±0.0474</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>0.5270±0.0706</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.4877±0.0522</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.3470±0.0531</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.1856±0.0360</t>
         </is>
@@ -917,100 +1577,320 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.3522±0.0463</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.3249±0.0658</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.3155±0.0780</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.4071±0.0622</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.9838±0.0042</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.9831±0.0036</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.9751±0.0042</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.9459±0.0070</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.5304±0.0697</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.5027±0.0530</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.4052±0.0439</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.2714±0.0359</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.5287±0.0701</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.5133±0.0553</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.4624±0.0437</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.3885±0.0486</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.5292±0.0699</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.5062±0.0535</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.4225±0.0422</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.3041±0.0382</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0.8531±0.0224</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0.8337±0.0152</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.7454±0.0317</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.6427±0.0259</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.5287±0.0701</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.5024±0.0523</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.4032±0.0435</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.2709±0.0359</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.1907±0.0548</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.2053±0.0784</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.2135±0.0552</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.1884±0.0368</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.1865±0.0491</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.2028±0.0962</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.1819±0.0623</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.1322±0.0274</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.2208±0.0610</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.2444±0.0720</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.3128±0.0664</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.3965±0.0922</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.9868±0.0315</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.9645±0.0491</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.9131±0.0652</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.5884±0.0795</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.5870±0.0513</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.5108±0.0365</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.3689±0.0390</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.5287±0.0701</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.4933±0.0537</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.3791±0.0349</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.2428±0.0303</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.6644±0.0959</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.7276±0.0565</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.7915±0.0725</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.7735±0.0601</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>0.8763±0.0288</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>0.8572±0.0279</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.7824±0.0354</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>0.6054±0.0480</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.5270±0.0706</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>0.4914±0.0506</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.3493±0.0529</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.1874±0.0368</t>
         </is>
@@ -1064,100 +1944,320 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.3503±0.0472</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.3196±0.0672</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.3171±0.0776</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.4105±0.0618</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.9839±0.0043</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.9830±0.0037</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.9750±0.0042</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.9453±0.0069</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.5326±0.0713</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.5020±0.0533</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.4043±0.0444</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.2698±0.0353</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.5331±0.0737</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.5156±0.0545</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.4629±0.0450</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.3898±0.0495</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.5322±0.0722</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.5065±0.0533</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.4219±0.0428</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.3031±0.0378</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.8538±0.0234</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0.8328±0.0158</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.7442±0.0323</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.6393±0.0256</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.5309±0.0718</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.5017±0.0526</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.4023±0.0439</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.2693±0.0354</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0.1940±0.0566</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.2071±0.0764</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.2131±0.0548</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.1870±0.0361</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.2031±0.0658</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.2010±0.0929</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.1815±0.0620</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.1310±0.0269</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.2226±0.0615</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.2491±0.0703</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.3132±0.0666</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.3972±0.0923</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.9845±0.0370</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.9626±0.0486</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.9112±0.0645</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.5916±0.0810</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.5869±0.0518</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.5099±0.0369</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.3671±0.0392</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.5305±0.0715</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.4916±0.0545</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.3779±0.0352</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.2411±0.0303</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.6696±0.0966</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.7312±0.0581</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.7922±0.0730</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.7744±0.0609</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>0.8763±0.0288</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>0.8562±0.0281</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.7818±0.0355</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>0.6044±0.0478</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.5270±0.0706</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>0.4877±0.0522</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.3475±0.0533</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.1852±0.0367</t>
         </is>
@@ -1211,100 +2311,320 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0.3569±0.0589</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.3885±0.0951</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.4328±0.0669</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.4884±0.0611</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.9842±0.0044</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.9762±0.0051</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.9473±0.0081</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.8381±0.0123</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>0.5261±0.0873</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.4823±0.0471</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.3740±0.0352</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.2408±0.0229</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.5261±0.0873</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.4921±0.0511</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.4426±0.0350</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.4753±0.0334</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.5261±0.0873</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.4849±0.0482</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.3952±0.0336</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0.3037±0.0252</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0.8594±0.0213</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0.8335±0.0184</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.7552±0.0220</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>0.6814±0.0193</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.5261±0.0873</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.4800±0.0469</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.3721±0.0348</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.2387±0.0227</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0.1781±0.0652</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.1863±0.0576</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.2050±0.0380</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.1867±0.0241</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.1633±0.0666</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.1921±0.0691</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.1709±0.0406</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.1297±0.0183</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.2152±0.0661</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.2220±0.0599</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.2967±0.0531</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.4079±0.0579</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.9946±0.0146</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.9854±0.0245</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.9297±0.0341</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.5928±0.0856</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.5637±0.0516</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.4632±0.0319</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.3262±0.0233</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.5244±0.0877</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.4723±0.0478</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.3489±0.0297</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.2160±0.0184</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.6844±0.0829</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.7008±0.0638</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.6912±0.0376</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.6685±0.0324</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.8742±0.0355</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>0.8012±0.0358</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.5779±0.0581</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>0.1194±0.0330</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>0.5261±0.0873</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>0.4659±0.0445</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>0.3065±0.0436</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.0817±0.0214</t>
         </is>
@@ -1358,100 +2678,320 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.3698±0.0691</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.3838±0.0953</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.4327±0.0690</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.4711±0.0625</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.9831±0.0043</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.9753±0.0050</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.9442±0.0091</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.8235±0.0126</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.5166±0.0739</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.4796±0.0456</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.3680±0.0370</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.2310±0.0187</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.5206±0.0770</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.4932±0.0462</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.4495±0.0409</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.5012±0.0391</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.5180±0.0748</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.4832±0.0451</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.3930±0.0364</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.3000±0.0225</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.8556±0.0193</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.8330±0.0160</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0.7520±0.0222</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>0.6622±0.0166</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.5166±0.0739</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.4768±0.0445</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.3662±0.0366</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.2291±0.0188</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.1801±0.0664</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.1917±0.0533</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.2068±0.0417</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.1888±0.0243</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.1769±0.0742</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.1887±0.0584</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.1712±0.0428</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.1282±0.0169</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.2172±0.0665</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.2300±0.0582</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.3021±0.0581</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.4392±0.0657</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.9901±0.0214</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.9832±0.0254</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.9173±0.0423</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.5866±0.0749</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.5629±0.0492</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.4605±0.0332</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.3208±0.0222</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.5145±0.0741</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.4683±0.0473</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.3429±0.0307</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.2089±0.0166</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.6838±0.0758</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.7076±0.0608</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.7030±0.0364</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.6937±0.0391</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>0.8650±0.0335</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>0.7924±0.0332</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.5547±0.0617</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.0984±0.0315</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>0.5127±0.0715</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>0.4579±0.0450</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.2911±0.0439</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.0652±0.0185</t>
         </is>
@@ -1505,100 +3045,320 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.3757±0.0568</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.3987±0.0936</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.4402±0.0645</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.4851±0.0598</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.9838±0.0043</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.9761±0.0050</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.9471±0.0084</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.8385±0.0125</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>0.5212±0.0751</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.4818±0.0494</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.3730±0.0359</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.2414±0.0239</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.5212±0.0751</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.4897±0.0509</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.4389±0.0366</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.4726±0.0352</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.5212±0.0751</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.4835±0.0494</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.3934±0.0349</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0.3035±0.0263</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0.8580±0.0187</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>0.8343±0.0169</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0.7552±0.0228</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>0.6817±0.0196</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.5212±0.0751</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.4789±0.0483</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.3711±0.0358</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.2395±0.0237</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>0.1762±0.0639</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.1833±0.0540</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.2038±0.0401</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.1867±0.0262</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.1606±0.0655</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.1862±0.0628</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.1708±0.0418</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.1300±0.0198</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.2154±0.0659</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.2188±0.0577</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.2926±0.0545</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.4060±0.0609</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.9951±0.0135</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.9842±0.0246</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.9284±0.0350</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.5913±0.0737</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.5632±0.0527</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.4616±0.0337</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.3254±0.0244</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.5195±0.0756</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.4721±0.0501</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.3478±0.0317</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>0.2158±0.0191</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.6889±0.0753</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0.7000±0.0639</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.6884±0.0386</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.6635±0.0351</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>0.8702±0.0347</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.8000±0.0347</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.5760±0.0585</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0.1225±0.0322</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>0.5212±0.0751</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>0.4653±0.0465</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.3075±0.0432</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.0847±0.0210</t>
         </is>
@@ -1652,100 +3412,320 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0.3875±0.0645</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.3883±0.0964</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.4360±0.0743</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.4682±0.0646</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.9830±0.0041</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.9752±0.0050</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.9439±0.0090</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.8230±0.0128</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.5139±0.0707</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.4786±0.0459</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.3654±0.0374</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.2307±0.0194</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.5178±0.0741</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.4917±0.0474</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.4459±0.0420</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.5005±0.0391</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.5152±0.0718</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.4820±0.0458</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.3901±0.0373</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.2995±0.0233</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.8547±0.0171</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.8323±0.0168</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.7509±0.0224</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>0.6608±0.0171</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.5139±0.0707</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.4757±0.0449</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.3635±0.0372</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.2288±0.0194</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.1794±0.0670</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.1914±0.0547</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.2051±0.0416</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.1875±0.0256</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.1759±0.0752</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.1901±0.0615</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.1698±0.0431</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.1274±0.0177</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.2172±0.0665</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.2292±0.0587</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.3007±0.0583</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.4368±0.0684</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.9902±0.0210</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.9819±0.0255</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.9170±0.0422</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.5843±0.0706</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.5616±0.0504</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.4579±0.0338</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.3196±0.0234</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.5118±0.0709</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.4674±0.0482</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.3409±0.0310</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.2081±0.0173</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.6820±0.0680</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.7057±0.0619</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.6999±0.0390</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.6908±0.0405</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>0.8640±0.0321</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>0.7924±0.0329</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.5521±0.0633</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0.1008±0.0328</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>0.5100±0.0681</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>0.4574±0.0446</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.2892±0.0434</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.0658±0.0190</t>
         </is>
